--- a/samples/tracking01/tracking01.xlsx
+++ b/samples/tracking01/tracking01.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frame_index</t>
+          <t>frame_index_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
